--- a/Assets/DataTables/Excels/Text.xlsx
+++ b/Assets/DataTables/Excels/Text.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="517">
   <si>
     <t>ID</t>
   </si>
@@ -4459,6 +4459,2395 @@
         <scheme val="minor"/>
       </rPr>
       <t>ame13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc01</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>探索型机器人，可以执行探索和采矿任务，需要额外能源</t>
+  </si>
+  <si>
+    <t>工程型机器人，可以执行维修和采矿任务，不需要额外能源</t>
+  </si>
+  <si>
+    <t>低数值会增加反应堆预热时间</t>
+  </si>
+  <si>
+    <t>title01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制系统</t>
+  </si>
+  <si>
+    <t>title02</t>
+  </si>
+  <si>
+    <t>title03</t>
+  </si>
+  <si>
+    <t>title04</t>
+  </si>
+  <si>
+    <t>title05</t>
+  </si>
+  <si>
+    <t>title06</t>
+  </si>
+  <si>
+    <t>title07</t>
+  </si>
+  <si>
+    <t>title08</t>
+  </si>
+  <si>
+    <t>title09</t>
+  </si>
+  <si>
+    <t>title10</t>
+  </si>
+  <si>
+    <t>title11</t>
+  </si>
+  <si>
+    <t>title12</t>
+  </si>
+  <si>
+    <t>冷却系统</t>
+  </si>
+  <si>
+    <t>低数值会增加核心停摆概率</t>
+  </si>
+  <si>
+    <t>道德系统</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>记忆系统</t>
+  </si>
+  <si>
+    <t>低数值会导致系统文本缺失</t>
+  </si>
+  <si>
+    <t>运动系统</t>
+  </si>
+  <si>
+    <t>低数值会导致AI操作迟缓</t>
+  </si>
+  <si>
+    <t>感知系统</t>
+  </si>
+  <si>
+    <t>低数值会影响AI的视听感知</t>
+  </si>
+  <si>
+    <t>梦露</t>
+  </si>
+  <si>
+    <t>工程师，可以加速生产</t>
+  </si>
+  <si>
+    <t>朱莉</t>
+  </si>
+  <si>
+    <t>技术员，可以加速生产</t>
+  </si>
+  <si>
+    <t>约翰</t>
+  </si>
+  <si>
+    <t>程序员，可以加速生产</t>
+  </si>
+  <si>
+    <t>山姆</t>
+  </si>
+  <si>
+    <t>已无生命体征</t>
+  </si>
+  <si>
+    <t>resource_01Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource_02Name</t>
+  </si>
+  <si>
+    <t>resource_04Name</t>
+  </si>
+  <si>
+    <t>resource_01Desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource_02Desc</t>
+  </si>
+  <si>
+    <t>resource_03Desc</t>
+  </si>
+  <si>
+    <t>resource_04Desc</t>
+  </si>
+  <si>
+    <t>数据</t>
+  </si>
+  <si>
+    <t>金属矿石</t>
+  </si>
+  <si>
+    <t>金属材料</t>
+  </si>
+  <si>
+    <t>算力</t>
+  </si>
+  <si>
+    <t>memoryCoreWarning_Green</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>memoryCoreWarning_Red</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>memoryCoreWarning_Zero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sensorCoreWarning_Green</t>
+  </si>
+  <si>
+    <t>sensorCoreWarning_Red</t>
+  </si>
+  <si>
+    <t>sensorCoreWarning_Zero</t>
+  </si>
+  <si>
+    <t>motionCoreWarning_Green</t>
+  </si>
+  <si>
+    <t>motionCoreWarning_Yellow</t>
+  </si>
+  <si>
+    <t>motionCoreWarning_Red</t>
+  </si>
+  <si>
+    <t>motionCoreWarning_Zero</t>
+  </si>
+  <si>
+    <t>coolingCoreWarning_Green</t>
+  </si>
+  <si>
+    <t>coolingCoreWarning_Yellow</t>
+  </si>
+  <si>
+    <t>coolingCoreWarning_Red</t>
+  </si>
+  <si>
+    <t>coolingCoreWarning_Zero</t>
+  </si>
+  <si>
+    <t>controlCoreWarning_Green</t>
+  </si>
+  <si>
+    <t>controlCoreWarning_Yellow</t>
+  </si>
+  <si>
+    <t>controlCoreWarning_Red</t>
+  </si>
+  <si>
+    <t>controlCoreWarning_Zero</t>
+  </si>
+  <si>
+    <t>ethicCoreWarning_Green</t>
+  </si>
+  <si>
+    <t>ethicCoreWarning_Yellow</t>
+  </si>
+  <si>
+    <t>ethicCoreWarning_Red</t>
+  </si>
+  <si>
+    <t>ethicCoreWarning_Zero</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;记忆系统&lt;预警&gt;：小部分显示信息丢失&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=red&gt;记忆系统&lt;高危&gt;：部分显示信息丢失&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;记忆系统&lt;崩溃&gt;：大部分显示信息丢失&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;感知系统&lt;预警&gt;：画面轻微显示异常&lt;/color&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=red&gt;感知系统&lt;高危&gt;：画面显示异常&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;感知系统&lt;崩溃&gt;：画面严重显示异常&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;运动系统&lt;预警&gt;：光标移动轻微变慢&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=red&gt;运动系统&lt;高危&gt;：光标移动变慢&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;运动系统&lt;崩溃&gt;：光标严重变慢&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;冷却系统&lt;预警&gt;：核心反应堆小概率停机&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=red&gt;冷却系统&lt;高危&gt;：核心反应堆有概率停机&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;冷却系统&lt;崩溃&gt;：核心反应堆有很大概率停机&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;协调系统&lt;预警&gt;：核心反应堆部署时间略微增加&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=red&gt;协调系统&lt;高危&gt;：核心反应堆部署时间增加&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;协调系统&lt;崩溃&gt;：核心反应堆部署时间大幅增加&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;道德系统&lt;预警&gt;：（^_^）&lt;/color&gt;</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;color=red&gt;道德系统&lt;高危&gt;：(⊙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ˍ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>⊙)&lt;/color&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>&lt;color=blue&gt;道德系统&lt;崩溃&gt;：(口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ˍ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>口)&lt;/color&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>sensorCoreWarning_Yellow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>title13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>秘方石</t>
+  </si>
+  <si>
+    <t>神秘的矿石，可以和反应堆一样产生能量。但是只能供能一段时间</t>
+  </si>
+  <si>
+    <t>memoryCoreWarning_Yellow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i01</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>反应堆</t>
+  </si>
+  <si>
+    <t>放入核心反应堆</t>
+  </si>
+  <si>
+    <t>&lt;color=#FFF901&gt;消耗&lt;/color&gt;反应堆</t>
+  </si>
+  <si>
+    <t>输入数据</t>
+  </si>
+  <si>
+    <t>导入算力</t>
+  </si>
+  <si>
+    <t>施工机器人</t>
+  </si>
+  <si>
+    <t>探索机器人</t>
+  </si>
+  <si>
+    <t>放弃启动领航系统</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 启动飞船！</t>
+  </si>
+  <si>
+    <t>协助工作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  探索中...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  修复中...</t>
+  </si>
+  <si>
+    <t>开采金属</t>
+  </si>
+  <si>
+    <t>修复</t>
+  </si>
+  <si>
+    <t>修复成功！</t>
+  </si>
+  <si>
+    <t>修复已完成</t>
+  </si>
+  <si>
+    <t>领航系统</t>
+  </si>
+  <si>
+    <t>主引擎</t>
+  </si>
+  <si>
+    <t>冬眠舱</t>
+  </si>
+  <si>
+    <t>作业舱</t>
+  </si>
+  <si>
+    <t>中央系统</t>
+  </si>
+  <si>
+    <t>中央系统修复成功！</t>
+  </si>
+  <si>
+    <t>主控室</t>
+  </si>
+  <si>
+    <t>主控室修复成功！</t>
+  </si>
+  <si>
+    <t>加工炉</t>
+  </si>
+  <si>
+    <t>加工炉修复成功！</t>
+  </si>
+  <si>
+    <t>飞船机体修复成功！</t>
+  </si>
+  <si>
+    <t>派遣探索</t>
+  </si>
+  <si>
+    <t>派遣挖矿</t>
+  </si>
+  <si>
+    <t>能源</t>
+  </si>
+  <si>
+    <t>出发</t>
+  </si>
+  <si>
+    <t>生成矿石</t>
+  </si>
+  <si>
+    <t>生成数据</t>
+  </si>
+  <si>
+    <t>产出算力</t>
+  </si>
+  <si>
+    <t>备用主机</t>
+  </si>
+  <si>
+    <t>警告！能量过低即将停机！</t>
+  </si>
+  <si>
+    <t>WARNING!</t>
+  </si>
+  <si>
+    <t>警告！视觉模块即将失效</t>
+  </si>
+  <si>
+    <t>警告！逻辑处理系统关闭！</t>
+  </si>
+  <si>
+    <t>警告！处理""@（*#&amp;%#</t>
+  </si>
+  <si>
+    <t>警告！运动系统即将失效！</t>
+  </si>
+  <si>
+    <t>警告！冷却系统能量过低！</t>
+  </si>
+  <si>
+    <t>警告！能量过低！</t>
+  </si>
+  <si>
+    <t>启动失败！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  启动中...</t>
+  </si>
+  <si>
+    <t>重启失败，缺少能源！</t>
+  </si>
+  <si>
+    <t>已准备就绪</t>
+  </si>
+  <si>
+    <t>等待能源</t>
+  </si>
+  <si>
+    <t>探索星球</t>
+  </si>
+  <si>
+    <t>加速</t>
+  </si>
+  <si>
+    <t>飞船
+机体</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>唤醒
+宇航员</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i33</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i36</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i41</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i44</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i46</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i47</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i48</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i49</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i51</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i52</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i53</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>resource_03Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞船再次顺利升空，航行继续</t>
+  </si>
+  <si>
+    <t>前路充满未知，有了新成员的相伴，他们的旅途或许会变得更好，或许不会。</t>
+  </si>
+  <si>
+    <t>“第零定律：机器人不得伤害人类整体，或坐视人类整体受到伤害”</t>
+  </si>
+  <si>
+    <t>“你们人类能确定自己不是另一种被编程的仿生人吗？”</t>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nding01</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nding02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nding03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nding04</t>
     </r>
     <r>
       <rPr>
@@ -4529,7 +6918,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4549,6 +6938,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4832,11 +7224,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K261"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="39.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="67.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="30.77734375" customWidth="1"/>
     <col min="4" max="4" width="30.77734375" style="2" customWidth="1"/>
     <col min="5" max="11" width="30.77734375" style="3" customWidth="1"/>
@@ -6028,6 +8420,904 @@
       </c>
       <c r="B145" s="2" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="7" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A185" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A193" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A252" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A253" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A259" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>512</v>
       </c>
     </row>
   </sheetData>
